--- a/excel/03_comidas.xlsx
+++ b/excel/03_comidas.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -49,9 +46,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -417,19 +413,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1261"/>
+  <dimension ref="A1:F1381"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>fecha</t>
         </is>
@@ -37785,7 +37781,7 @@
       </c>
       <c r="E1253" t="inlineStr">
         <is>
-          <t>vacio</t>
+          <t>no_dado</t>
         </is>
       </c>
       <c r="F1253" t="inlineStr">
@@ -37815,7 +37811,7 @@
       </c>
       <c r="E1254" t="inlineStr">
         <is>
-          <t>vacio</t>
+          <t>no_dado</t>
         </is>
       </c>
       <c r="F1254" t="inlineStr">
@@ -37845,7 +37841,7 @@
       </c>
       <c r="E1255" t="inlineStr">
         <is>
-          <t>vacio</t>
+          <t>no_dado</t>
         </is>
       </c>
       <c r="F1255" t="inlineStr">
@@ -37875,7 +37871,7 @@
       </c>
       <c r="E1256" t="inlineStr">
         <is>
-          <t>vacio</t>
+          <t>no_dado</t>
         </is>
       </c>
       <c r="F1256" t="inlineStr">
@@ -37905,7 +37901,7 @@
       </c>
       <c r="E1257" t="inlineStr">
         <is>
-          <t>vacio</t>
+          <t>dado</t>
         </is>
       </c>
       <c r="F1257" t="inlineStr">
@@ -37933,7 +37929,7 @@
       <c r="D1258" t="inlineStr"/>
       <c r="E1258" t="inlineStr">
         <is>
-          <t>vacio</t>
+          <t>no_dado</t>
         </is>
       </c>
       <c r="F1258" t="inlineStr">
@@ -37963,7 +37959,7 @@
       </c>
       <c r="E1259" t="inlineStr">
         <is>
-          <t>vacio</t>
+          <t>dado</t>
         </is>
       </c>
       <c r="F1259" t="inlineStr">
@@ -37993,7 +37989,7 @@
       </c>
       <c r="E1260" t="inlineStr">
         <is>
-          <t>vacio</t>
+          <t>dado</t>
         </is>
       </c>
       <c r="F1260" t="inlineStr">
@@ -38023,12 +38019,3588 @@
       </c>
       <c r="E1261" t="inlineStr">
         <is>
-          <t>vacio</t>
+          <t>dado</t>
         </is>
       </c>
       <c r="F1261" t="inlineStr">
         <is>
           <t>orig39</t>
+        </is>
+      </c>
+    </row>
+    <row r="1262">
+      <c r="A1262" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B1262" t="inlineStr">
+        <is>
+          <t>mediodia</t>
+        </is>
+      </c>
+      <c r="C1262" t="inlineStr">
+        <is>
+          <t>PECHUGA</t>
+        </is>
+      </c>
+      <c r="D1262" t="n">
+        <v>100</v>
+      </c>
+      <c r="E1262" t="inlineStr">
+        <is>
+          <t>no_dado</t>
+        </is>
+      </c>
+      <c r="F1262" t="inlineStr">
+        <is>
+          <t>usuario</t>
+        </is>
+      </c>
+    </row>
+    <row r="1263">
+      <c r="A1263" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B1263" t="inlineStr">
+        <is>
+          <t>mediodia</t>
+        </is>
+      </c>
+      <c r="C1263" t="inlineStr">
+        <is>
+          <t>MUSLO</t>
+        </is>
+      </c>
+      <c r="D1263" t="n">
+        <v>25</v>
+      </c>
+      <c r="E1263" t="inlineStr">
+        <is>
+          <t>no_dado</t>
+        </is>
+      </c>
+      <c r="F1263" t="inlineStr">
+        <is>
+          <t>usuario</t>
+        </is>
+      </c>
+    </row>
+    <row r="1264">
+      <c r="A1264" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B1264" t="inlineStr">
+        <is>
+          <t>mediodia</t>
+        </is>
+      </c>
+      <c r="C1264" t="inlineStr">
+        <is>
+          <t>ZAPALLITO</t>
+        </is>
+      </c>
+      <c r="D1264" t="n">
+        <v>25</v>
+      </c>
+      <c r="E1264" t="inlineStr">
+        <is>
+          <t>no_dado</t>
+        </is>
+      </c>
+      <c r="F1264" t="inlineStr">
+        <is>
+          <t>usuario</t>
+        </is>
+      </c>
+    </row>
+    <row r="1265">
+      <c r="A1265" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B1265" t="inlineStr">
+        <is>
+          <t>mediodia</t>
+        </is>
+      </c>
+      <c r="C1265" t="inlineStr">
+        <is>
+          <t>ARROZ</t>
+        </is>
+      </c>
+      <c r="D1265" t="n">
+        <v>25</v>
+      </c>
+      <c r="E1265" t="inlineStr">
+        <is>
+          <t>no_dado</t>
+        </is>
+      </c>
+      <c r="F1265" t="inlineStr">
+        <is>
+          <t>usuario</t>
+        </is>
+      </c>
+    </row>
+    <row r="1266">
+      <c r="A1266" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B1266" t="inlineStr">
+        <is>
+          <t>mediodia</t>
+        </is>
+      </c>
+      <c r="C1266" t="inlineStr">
+        <is>
+          <t>JUREL</t>
+        </is>
+      </c>
+      <c r="D1266" t="n">
+        <v>25</v>
+      </c>
+      <c r="E1266" t="inlineStr">
+        <is>
+          <t>no_dado</t>
+        </is>
+      </c>
+      <c r="F1266" t="inlineStr">
+        <is>
+          <t>usuario</t>
+        </is>
+      </c>
+    </row>
+    <row r="1267">
+      <c r="A1267" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B1267" t="inlineStr">
+        <is>
+          <t>mediodia</t>
+        </is>
+      </c>
+      <c r="C1267" t="inlineStr">
+        <is>
+          <t>CALCIVET</t>
+        </is>
+      </c>
+      <c r="D1267" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E1267" t="inlineStr">
+        <is>
+          <t>dado</t>
+        </is>
+      </c>
+      <c r="F1267" t="inlineStr">
+        <is>
+          <t>usuario</t>
+        </is>
+      </c>
+    </row>
+    <row r="1268">
+      <c r="A1268" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B1268" t="inlineStr">
+        <is>
+          <t>mediodia</t>
+        </is>
+      </c>
+      <c r="C1268" t="inlineStr">
+        <is>
+          <t>TAURINA</t>
+        </is>
+      </c>
+      <c r="D1268" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="E1268" t="inlineStr">
+        <is>
+          <t>dado</t>
+        </is>
+      </c>
+      <c r="F1268" t="inlineStr">
+        <is>
+          <t>usuario</t>
+        </is>
+      </c>
+    </row>
+    <row r="1269">
+      <c r="A1269" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B1269" t="inlineStr">
+        <is>
+          <t>mediodia</t>
+        </is>
+      </c>
+      <c r="C1269" t="inlineStr">
+        <is>
+          <t>SOPA_MORO</t>
+        </is>
+      </c>
+      <c r="D1269" t="inlineStr"/>
+      <c r="E1269" t="inlineStr">
+        <is>
+          <t>no_dado</t>
+        </is>
+      </c>
+      <c r="F1269" t="inlineStr">
+        <is>
+          <t>usuario</t>
+        </is>
+      </c>
+    </row>
+    <row r="1270">
+      <c r="A1270" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B1270" t="inlineStr">
+        <is>
+          <t>mediodia</t>
+        </is>
+      </c>
+      <c r="C1270" t="inlineStr">
+        <is>
+          <t>MANZANA</t>
+        </is>
+      </c>
+      <c r="D1270" t="n">
+        <v>20</v>
+      </c>
+      <c r="E1270" t="inlineStr">
+        <is>
+          <t>dado</t>
+        </is>
+      </c>
+      <c r="F1270" t="inlineStr">
+        <is>
+          <t>usuario</t>
+        </is>
+      </c>
+    </row>
+    <row r="1271">
+      <c r="A1271" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B1271" t="inlineStr">
+        <is>
+          <t>mediodia</t>
+        </is>
+      </c>
+      <c r="C1271" t="inlineStr">
+        <is>
+          <t>BONIATO</t>
+        </is>
+      </c>
+      <c r="D1271" t="n">
+        <v>25</v>
+      </c>
+      <c r="E1271" t="inlineStr">
+        <is>
+          <t>dado</t>
+        </is>
+      </c>
+      <c r="F1271" t="inlineStr">
+        <is>
+          <t>usuario</t>
+        </is>
+      </c>
+    </row>
+    <row r="1272">
+      <c r="A1272" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B1272" t="inlineStr">
+        <is>
+          <t>mediodia</t>
+        </is>
+      </c>
+      <c r="C1272" t="inlineStr">
+        <is>
+          <t>CERDO</t>
+        </is>
+      </c>
+      <c r="D1272" t="n">
+        <v>125</v>
+      </c>
+      <c r="E1272" t="inlineStr">
+        <is>
+          <t>dado</t>
+        </is>
+      </c>
+      <c r="F1272" t="inlineStr">
+        <is>
+          <t>usuario</t>
+        </is>
+      </c>
+    </row>
+    <row r="1273">
+      <c r="A1273" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B1273" t="inlineStr">
+        <is>
+          <t>medianoche</t>
+        </is>
+      </c>
+      <c r="C1273" t="inlineStr">
+        <is>
+          <t>PECHUGA</t>
+        </is>
+      </c>
+      <c r="D1273" t="n">
+        <v>100</v>
+      </c>
+      <c r="E1273" t="inlineStr">
+        <is>
+          <t>no_dado</t>
+        </is>
+      </c>
+      <c r="F1273" t="inlineStr">
+        <is>
+          <t>usuario</t>
+        </is>
+      </c>
+    </row>
+    <row r="1274">
+      <c r="A1274" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B1274" t="inlineStr">
+        <is>
+          <t>medianoche</t>
+        </is>
+      </c>
+      <c r="C1274" t="inlineStr">
+        <is>
+          <t>MUSLO</t>
+        </is>
+      </c>
+      <c r="D1274" t="n">
+        <v>25</v>
+      </c>
+      <c r="E1274" t="inlineStr">
+        <is>
+          <t>no_dado</t>
+        </is>
+      </c>
+      <c r="F1274" t="inlineStr">
+        <is>
+          <t>usuario</t>
+        </is>
+      </c>
+    </row>
+    <row r="1275">
+      <c r="A1275" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B1275" t="inlineStr">
+        <is>
+          <t>medianoche</t>
+        </is>
+      </c>
+      <c r="C1275" t="inlineStr">
+        <is>
+          <t>ZAPALLITO</t>
+        </is>
+      </c>
+      <c r="D1275" t="n">
+        <v>25</v>
+      </c>
+      <c r="E1275" t="inlineStr">
+        <is>
+          <t>no_dado</t>
+        </is>
+      </c>
+      <c r="F1275" t="inlineStr">
+        <is>
+          <t>usuario</t>
+        </is>
+      </c>
+    </row>
+    <row r="1276">
+      <c r="A1276" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B1276" t="inlineStr">
+        <is>
+          <t>medianoche</t>
+        </is>
+      </c>
+      <c r="C1276" t="inlineStr">
+        <is>
+          <t>ARROZ</t>
+        </is>
+      </c>
+      <c r="D1276" t="n">
+        <v>25</v>
+      </c>
+      <c r="E1276" t="inlineStr">
+        <is>
+          <t>no_dado</t>
+        </is>
+      </c>
+      <c r="F1276" t="inlineStr">
+        <is>
+          <t>usuario</t>
+        </is>
+      </c>
+    </row>
+    <row r="1277">
+      <c r="A1277" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B1277" t="inlineStr">
+        <is>
+          <t>medianoche</t>
+        </is>
+      </c>
+      <c r="C1277" t="inlineStr">
+        <is>
+          <t>CALCIVET</t>
+        </is>
+      </c>
+      <c r="D1277" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E1277" t="inlineStr">
+        <is>
+          <t>dado</t>
+        </is>
+      </c>
+      <c r="F1277" t="inlineStr">
+        <is>
+          <t>usuario</t>
+        </is>
+      </c>
+    </row>
+    <row r="1278">
+      <c r="A1278" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B1278" t="inlineStr">
+        <is>
+          <t>medianoche</t>
+        </is>
+      </c>
+      <c r="C1278" t="inlineStr">
+        <is>
+          <t>SOPA_MORO</t>
+        </is>
+      </c>
+      <c r="D1278" t="inlineStr"/>
+      <c r="E1278" t="inlineStr">
+        <is>
+          <t>no_dado</t>
+        </is>
+      </c>
+      <c r="F1278" t="inlineStr">
+        <is>
+          <t>usuario</t>
+        </is>
+      </c>
+    </row>
+    <row r="1279">
+      <c r="A1279" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B1279" t="inlineStr">
+        <is>
+          <t>medianoche</t>
+        </is>
+      </c>
+      <c r="C1279" t="inlineStr">
+        <is>
+          <t>MANZANA</t>
+        </is>
+      </c>
+      <c r="D1279" t="n">
+        <v>20</v>
+      </c>
+      <c r="E1279" t="inlineStr">
+        <is>
+          <t>dado</t>
+        </is>
+      </c>
+      <c r="F1279" t="inlineStr">
+        <is>
+          <t>usuario</t>
+        </is>
+      </c>
+    </row>
+    <row r="1280">
+      <c r="A1280" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B1280" t="inlineStr">
+        <is>
+          <t>medianoche</t>
+        </is>
+      </c>
+      <c r="C1280" t="inlineStr">
+        <is>
+          <t>BONIATO</t>
+        </is>
+      </c>
+      <c r="D1280" t="n">
+        <v>25</v>
+      </c>
+      <c r="E1280" t="inlineStr">
+        <is>
+          <t>dado</t>
+        </is>
+      </c>
+      <c r="F1280" t="inlineStr">
+        <is>
+          <t>usuario</t>
+        </is>
+      </c>
+    </row>
+    <row r="1281">
+      <c r="A1281" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B1281" t="inlineStr">
+        <is>
+          <t>medianoche</t>
+        </is>
+      </c>
+      <c r="C1281" t="inlineStr">
+        <is>
+          <t>CERDO</t>
+        </is>
+      </c>
+      <c r="D1281" t="n">
+        <v>125</v>
+      </c>
+      <c r="E1281" t="inlineStr">
+        <is>
+          <t>dado</t>
+        </is>
+      </c>
+      <c r="F1281" t="inlineStr">
+        <is>
+          <t>usuario</t>
+        </is>
+      </c>
+    </row>
+    <row r="1282">
+      <c r="A1282" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B1282" t="inlineStr">
+        <is>
+          <t>mediodia</t>
+        </is>
+      </c>
+      <c r="C1282" t="inlineStr">
+        <is>
+          <t>PECHUGA</t>
+        </is>
+      </c>
+      <c r="D1282" t="n">
+        <v>100</v>
+      </c>
+      <c r="E1282" t="inlineStr">
+        <is>
+          <t>no_dado</t>
+        </is>
+      </c>
+      <c r="F1282" t="inlineStr">
+        <is>
+          <t>usuario</t>
+        </is>
+      </c>
+    </row>
+    <row r="1283">
+      <c r="A1283" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B1283" t="inlineStr">
+        <is>
+          <t>mediodia</t>
+        </is>
+      </c>
+      <c r="C1283" t="inlineStr">
+        <is>
+          <t>MUSLO</t>
+        </is>
+      </c>
+      <c r="D1283" t="n">
+        <v>25</v>
+      </c>
+      <c r="E1283" t="inlineStr">
+        <is>
+          <t>no_dado</t>
+        </is>
+      </c>
+      <c r="F1283" t="inlineStr">
+        <is>
+          <t>usuario</t>
+        </is>
+      </c>
+    </row>
+    <row r="1284">
+      <c r="A1284" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B1284" t="inlineStr">
+        <is>
+          <t>mediodia</t>
+        </is>
+      </c>
+      <c r="C1284" t="inlineStr">
+        <is>
+          <t>ZAPALLITO</t>
+        </is>
+      </c>
+      <c r="D1284" t="n">
+        <v>25</v>
+      </c>
+      <c r="E1284" t="inlineStr">
+        <is>
+          <t>no_dado</t>
+        </is>
+      </c>
+      <c r="F1284" t="inlineStr">
+        <is>
+          <t>usuario</t>
+        </is>
+      </c>
+    </row>
+    <row r="1285">
+      <c r="A1285" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B1285" t="inlineStr">
+        <is>
+          <t>mediodia</t>
+        </is>
+      </c>
+      <c r="C1285" t="inlineStr">
+        <is>
+          <t>ARROZ</t>
+        </is>
+      </c>
+      <c r="D1285" t="n">
+        <v>25</v>
+      </c>
+      <c r="E1285" t="inlineStr">
+        <is>
+          <t>no_dado</t>
+        </is>
+      </c>
+      <c r="F1285" t="inlineStr">
+        <is>
+          <t>usuario</t>
+        </is>
+      </c>
+    </row>
+    <row r="1286">
+      <c r="A1286" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B1286" t="inlineStr">
+        <is>
+          <t>mediodia</t>
+        </is>
+      </c>
+      <c r="C1286" t="inlineStr">
+        <is>
+          <t>JUREL</t>
+        </is>
+      </c>
+      <c r="D1286" t="n">
+        <v>25</v>
+      </c>
+      <c r="E1286" t="inlineStr">
+        <is>
+          <t>no_dado</t>
+        </is>
+      </c>
+      <c r="F1286" t="inlineStr">
+        <is>
+          <t>usuario</t>
+        </is>
+      </c>
+    </row>
+    <row r="1287">
+      <c r="A1287" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B1287" t="inlineStr">
+        <is>
+          <t>mediodia</t>
+        </is>
+      </c>
+      <c r="C1287" t="inlineStr">
+        <is>
+          <t>CALCIVET</t>
+        </is>
+      </c>
+      <c r="D1287" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E1287" t="inlineStr">
+        <is>
+          <t>dado</t>
+        </is>
+      </c>
+      <c r="F1287" t="inlineStr">
+        <is>
+          <t>usuario</t>
+        </is>
+      </c>
+    </row>
+    <row r="1288">
+      <c r="A1288" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B1288" t="inlineStr">
+        <is>
+          <t>mediodia</t>
+        </is>
+      </c>
+      <c r="C1288" t="inlineStr">
+        <is>
+          <t>TAURINA</t>
+        </is>
+      </c>
+      <c r="D1288" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="E1288" t="inlineStr">
+        <is>
+          <t>dado</t>
+        </is>
+      </c>
+      <c r="F1288" t="inlineStr">
+        <is>
+          <t>usuario</t>
+        </is>
+      </c>
+    </row>
+    <row r="1289">
+      <c r="A1289" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B1289" t="inlineStr">
+        <is>
+          <t>mediodia</t>
+        </is>
+      </c>
+      <c r="C1289" t="inlineStr">
+        <is>
+          <t>SOPA_MORO</t>
+        </is>
+      </c>
+      <c r="D1289" t="inlineStr"/>
+      <c r="E1289" t="inlineStr">
+        <is>
+          <t>no_dado</t>
+        </is>
+      </c>
+      <c r="F1289" t="inlineStr">
+        <is>
+          <t>usuario</t>
+        </is>
+      </c>
+    </row>
+    <row r="1290">
+      <c r="A1290" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B1290" t="inlineStr">
+        <is>
+          <t>mediodia</t>
+        </is>
+      </c>
+      <c r="C1290" t="inlineStr">
+        <is>
+          <t>MANZANA</t>
+        </is>
+      </c>
+      <c r="D1290" t="n">
+        <v>20</v>
+      </c>
+      <c r="E1290" t="inlineStr">
+        <is>
+          <t>dado</t>
+        </is>
+      </c>
+      <c r="F1290" t="inlineStr">
+        <is>
+          <t>usuario</t>
+        </is>
+      </c>
+    </row>
+    <row r="1291">
+      <c r="A1291" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B1291" t="inlineStr">
+        <is>
+          <t>mediodia</t>
+        </is>
+      </c>
+      <c r="C1291" t="inlineStr">
+        <is>
+          <t>BONIATO</t>
+        </is>
+      </c>
+      <c r="D1291" t="n">
+        <v>25</v>
+      </c>
+      <c r="E1291" t="inlineStr">
+        <is>
+          <t>dado</t>
+        </is>
+      </c>
+      <c r="F1291" t="inlineStr">
+        <is>
+          <t>usuario</t>
+        </is>
+      </c>
+    </row>
+    <row r="1292">
+      <c r="A1292" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B1292" t="inlineStr">
+        <is>
+          <t>mediodia</t>
+        </is>
+      </c>
+      <c r="C1292" t="inlineStr">
+        <is>
+          <t>CERDO</t>
+        </is>
+      </c>
+      <c r="D1292" t="n">
+        <v>125</v>
+      </c>
+      <c r="E1292" t="inlineStr">
+        <is>
+          <t>dado</t>
+        </is>
+      </c>
+      <c r="F1292" t="inlineStr">
+        <is>
+          <t>usuario</t>
+        </is>
+      </c>
+    </row>
+    <row r="1293">
+      <c r="A1293" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B1293" t="inlineStr">
+        <is>
+          <t>medianoche</t>
+        </is>
+      </c>
+      <c r="C1293" t="inlineStr">
+        <is>
+          <t>PECHUGA</t>
+        </is>
+      </c>
+      <c r="D1293" t="n">
+        <v>100</v>
+      </c>
+      <c r="E1293" t="inlineStr">
+        <is>
+          <t>no_dado</t>
+        </is>
+      </c>
+      <c r="F1293" t="inlineStr">
+        <is>
+          <t>usuario</t>
+        </is>
+      </c>
+    </row>
+    <row r="1294">
+      <c r="A1294" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B1294" t="inlineStr">
+        <is>
+          <t>medianoche</t>
+        </is>
+      </c>
+      <c r="C1294" t="inlineStr">
+        <is>
+          <t>MUSLO</t>
+        </is>
+      </c>
+      <c r="D1294" t="n">
+        <v>25</v>
+      </c>
+      <c r="E1294" t="inlineStr">
+        <is>
+          <t>no_dado</t>
+        </is>
+      </c>
+      <c r="F1294" t="inlineStr">
+        <is>
+          <t>usuario</t>
+        </is>
+      </c>
+    </row>
+    <row r="1295">
+      <c r="A1295" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B1295" t="inlineStr">
+        <is>
+          <t>medianoche</t>
+        </is>
+      </c>
+      <c r="C1295" t="inlineStr">
+        <is>
+          <t>ZAPALLITO</t>
+        </is>
+      </c>
+      <c r="D1295" t="n">
+        <v>25</v>
+      </c>
+      <c r="E1295" t="inlineStr">
+        <is>
+          <t>no_dado</t>
+        </is>
+      </c>
+      <c r="F1295" t="inlineStr">
+        <is>
+          <t>usuario</t>
+        </is>
+      </c>
+    </row>
+    <row r="1296">
+      <c r="A1296" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B1296" t="inlineStr">
+        <is>
+          <t>medianoche</t>
+        </is>
+      </c>
+      <c r="C1296" t="inlineStr">
+        <is>
+          <t>ARROZ</t>
+        </is>
+      </c>
+      <c r="D1296" t="n">
+        <v>25</v>
+      </c>
+      <c r="E1296" t="inlineStr">
+        <is>
+          <t>no_dado</t>
+        </is>
+      </c>
+      <c r="F1296" t="inlineStr">
+        <is>
+          <t>usuario</t>
+        </is>
+      </c>
+    </row>
+    <row r="1297">
+      <c r="A1297" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B1297" t="inlineStr">
+        <is>
+          <t>medianoche</t>
+        </is>
+      </c>
+      <c r="C1297" t="inlineStr">
+        <is>
+          <t>CALCIVET</t>
+        </is>
+      </c>
+      <c r="D1297" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E1297" t="inlineStr">
+        <is>
+          <t>dado</t>
+        </is>
+      </c>
+      <c r="F1297" t="inlineStr">
+        <is>
+          <t>usuario</t>
+        </is>
+      </c>
+    </row>
+    <row r="1298">
+      <c r="A1298" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B1298" t="inlineStr">
+        <is>
+          <t>medianoche</t>
+        </is>
+      </c>
+      <c r="C1298" t="inlineStr">
+        <is>
+          <t>SOPA_MORO</t>
+        </is>
+      </c>
+      <c r="D1298" t="inlineStr"/>
+      <c r="E1298" t="inlineStr">
+        <is>
+          <t>no_dado</t>
+        </is>
+      </c>
+      <c r="F1298" t="inlineStr">
+        <is>
+          <t>usuario</t>
+        </is>
+      </c>
+    </row>
+    <row r="1299">
+      <c r="A1299" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B1299" t="inlineStr">
+        <is>
+          <t>medianoche</t>
+        </is>
+      </c>
+      <c r="C1299" t="inlineStr">
+        <is>
+          <t>MANZANA</t>
+        </is>
+      </c>
+      <c r="D1299" t="n">
+        <v>20</v>
+      </c>
+      <c r="E1299" t="inlineStr">
+        <is>
+          <t>dado</t>
+        </is>
+      </c>
+      <c r="F1299" t="inlineStr">
+        <is>
+          <t>usuario</t>
+        </is>
+      </c>
+    </row>
+    <row r="1300">
+      <c r="A1300" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B1300" t="inlineStr">
+        <is>
+          <t>medianoche</t>
+        </is>
+      </c>
+      <c r="C1300" t="inlineStr">
+        <is>
+          <t>BONIATO</t>
+        </is>
+      </c>
+      <c r="D1300" t="n">
+        <v>25</v>
+      </c>
+      <c r="E1300" t="inlineStr">
+        <is>
+          <t>dado</t>
+        </is>
+      </c>
+      <c r="F1300" t="inlineStr">
+        <is>
+          <t>usuario</t>
+        </is>
+      </c>
+    </row>
+    <row r="1301">
+      <c r="A1301" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B1301" t="inlineStr">
+        <is>
+          <t>medianoche</t>
+        </is>
+      </c>
+      <c r="C1301" t="inlineStr">
+        <is>
+          <t>CERDO</t>
+        </is>
+      </c>
+      <c r="D1301" t="n">
+        <v>125</v>
+      </c>
+      <c r="E1301" t="inlineStr">
+        <is>
+          <t>dado</t>
+        </is>
+      </c>
+      <c r="F1301" t="inlineStr">
+        <is>
+          <t>usuario</t>
+        </is>
+      </c>
+    </row>
+    <row r="1302">
+      <c r="A1302" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B1302" t="inlineStr">
+        <is>
+          <t>mediodia</t>
+        </is>
+      </c>
+      <c r="C1302" t="inlineStr">
+        <is>
+          <t>PECHUGA</t>
+        </is>
+      </c>
+      <c r="D1302" t="n">
+        <v>100</v>
+      </c>
+      <c r="E1302" t="inlineStr">
+        <is>
+          <t>no_dado</t>
+        </is>
+      </c>
+      <c r="F1302" t="inlineStr">
+        <is>
+          <t>usuario</t>
+        </is>
+      </c>
+    </row>
+    <row r="1303">
+      <c r="A1303" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B1303" t="inlineStr">
+        <is>
+          <t>mediodia</t>
+        </is>
+      </c>
+      <c r="C1303" t="inlineStr">
+        <is>
+          <t>MUSLO</t>
+        </is>
+      </c>
+      <c r="D1303" t="n">
+        <v>25</v>
+      </c>
+      <c r="E1303" t="inlineStr">
+        <is>
+          <t>no_dado</t>
+        </is>
+      </c>
+      <c r="F1303" t="inlineStr">
+        <is>
+          <t>usuario</t>
+        </is>
+      </c>
+    </row>
+    <row r="1304">
+      <c r="A1304" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B1304" t="inlineStr">
+        <is>
+          <t>mediodia</t>
+        </is>
+      </c>
+      <c r="C1304" t="inlineStr">
+        <is>
+          <t>ZAPALLITO</t>
+        </is>
+      </c>
+      <c r="D1304" t="n">
+        <v>25</v>
+      </c>
+      <c r="E1304" t="inlineStr">
+        <is>
+          <t>no_dado</t>
+        </is>
+      </c>
+      <c r="F1304" t="inlineStr">
+        <is>
+          <t>usuario</t>
+        </is>
+      </c>
+    </row>
+    <row r="1305">
+      <c r="A1305" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B1305" t="inlineStr">
+        <is>
+          <t>mediodia</t>
+        </is>
+      </c>
+      <c r="C1305" t="inlineStr">
+        <is>
+          <t>ARROZ</t>
+        </is>
+      </c>
+      <c r="D1305" t="n">
+        <v>25</v>
+      </c>
+      <c r="E1305" t="inlineStr">
+        <is>
+          <t>no_dado</t>
+        </is>
+      </c>
+      <c r="F1305" t="inlineStr">
+        <is>
+          <t>usuario</t>
+        </is>
+      </c>
+    </row>
+    <row r="1306">
+      <c r="A1306" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B1306" t="inlineStr">
+        <is>
+          <t>mediodia</t>
+        </is>
+      </c>
+      <c r="C1306" t="inlineStr">
+        <is>
+          <t>JUREL</t>
+        </is>
+      </c>
+      <c r="D1306" t="n">
+        <v>25</v>
+      </c>
+      <c r="E1306" t="inlineStr">
+        <is>
+          <t>no_dado</t>
+        </is>
+      </c>
+      <c r="F1306" t="inlineStr">
+        <is>
+          <t>usuario</t>
+        </is>
+      </c>
+    </row>
+    <row r="1307">
+      <c r="A1307" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B1307" t="inlineStr">
+        <is>
+          <t>mediodia</t>
+        </is>
+      </c>
+      <c r="C1307" t="inlineStr">
+        <is>
+          <t>CALCIVET</t>
+        </is>
+      </c>
+      <c r="D1307" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E1307" t="inlineStr">
+        <is>
+          <t>dado</t>
+        </is>
+      </c>
+      <c r="F1307" t="inlineStr">
+        <is>
+          <t>usuario</t>
+        </is>
+      </c>
+    </row>
+    <row r="1308">
+      <c r="A1308" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B1308" t="inlineStr">
+        <is>
+          <t>mediodia</t>
+        </is>
+      </c>
+      <c r="C1308" t="inlineStr">
+        <is>
+          <t>TAURINA</t>
+        </is>
+      </c>
+      <c r="D1308" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="E1308" t="inlineStr">
+        <is>
+          <t>dado</t>
+        </is>
+      </c>
+      <c r="F1308" t="inlineStr">
+        <is>
+          <t>usuario</t>
+        </is>
+      </c>
+    </row>
+    <row r="1309">
+      <c r="A1309" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B1309" t="inlineStr">
+        <is>
+          <t>mediodia</t>
+        </is>
+      </c>
+      <c r="C1309" t="inlineStr">
+        <is>
+          <t>SOPA_MORO</t>
+        </is>
+      </c>
+      <c r="D1309" t="inlineStr"/>
+      <c r="E1309" t="inlineStr">
+        <is>
+          <t>no_dado</t>
+        </is>
+      </c>
+      <c r="F1309" t="inlineStr">
+        <is>
+          <t>usuario</t>
+        </is>
+      </c>
+    </row>
+    <row r="1310">
+      <c r="A1310" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B1310" t="inlineStr">
+        <is>
+          <t>mediodia</t>
+        </is>
+      </c>
+      <c r="C1310" t="inlineStr">
+        <is>
+          <t>MANZANA</t>
+        </is>
+      </c>
+      <c r="D1310" t="n">
+        <v>20</v>
+      </c>
+      <c r="E1310" t="inlineStr">
+        <is>
+          <t>dado</t>
+        </is>
+      </c>
+      <c r="F1310" t="inlineStr">
+        <is>
+          <t>usuario</t>
+        </is>
+      </c>
+    </row>
+    <row r="1311">
+      <c r="A1311" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B1311" t="inlineStr">
+        <is>
+          <t>mediodia</t>
+        </is>
+      </c>
+      <c r="C1311" t="inlineStr">
+        <is>
+          <t>BONIATO</t>
+        </is>
+      </c>
+      <c r="D1311" t="n">
+        <v>25</v>
+      </c>
+      <c r="E1311" t="inlineStr">
+        <is>
+          <t>dado</t>
+        </is>
+      </c>
+      <c r="F1311" t="inlineStr">
+        <is>
+          <t>usuario</t>
+        </is>
+      </c>
+    </row>
+    <row r="1312">
+      <c r="A1312" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B1312" t="inlineStr">
+        <is>
+          <t>mediodia</t>
+        </is>
+      </c>
+      <c r="C1312" t="inlineStr">
+        <is>
+          <t>CERDO</t>
+        </is>
+      </c>
+      <c r="D1312" t="n">
+        <v>125</v>
+      </c>
+      <c r="E1312" t="inlineStr">
+        <is>
+          <t>dado</t>
+        </is>
+      </c>
+      <c r="F1312" t="inlineStr">
+        <is>
+          <t>usuario</t>
+        </is>
+      </c>
+    </row>
+    <row r="1313">
+      <c r="A1313" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B1313" t="inlineStr">
+        <is>
+          <t>medianoche</t>
+        </is>
+      </c>
+      <c r="C1313" t="inlineStr">
+        <is>
+          <t>PECHUGA</t>
+        </is>
+      </c>
+      <c r="D1313" t="n">
+        <v>100</v>
+      </c>
+      <c r="E1313" t="inlineStr">
+        <is>
+          <t>no_dado</t>
+        </is>
+      </c>
+      <c r="F1313" t="inlineStr">
+        <is>
+          <t>usuario</t>
+        </is>
+      </c>
+    </row>
+    <row r="1314">
+      <c r="A1314" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B1314" t="inlineStr">
+        <is>
+          <t>medianoche</t>
+        </is>
+      </c>
+      <c r="C1314" t="inlineStr">
+        <is>
+          <t>MUSLO</t>
+        </is>
+      </c>
+      <c r="D1314" t="n">
+        <v>25</v>
+      </c>
+      <c r="E1314" t="inlineStr">
+        <is>
+          <t>no_dado</t>
+        </is>
+      </c>
+      <c r="F1314" t="inlineStr">
+        <is>
+          <t>usuario</t>
+        </is>
+      </c>
+    </row>
+    <row r="1315">
+      <c r="A1315" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B1315" t="inlineStr">
+        <is>
+          <t>medianoche</t>
+        </is>
+      </c>
+      <c r="C1315" t="inlineStr">
+        <is>
+          <t>ZAPALLITO</t>
+        </is>
+      </c>
+      <c r="D1315" t="n">
+        <v>25</v>
+      </c>
+      <c r="E1315" t="inlineStr">
+        <is>
+          <t>no_dado</t>
+        </is>
+      </c>
+      <c r="F1315" t="inlineStr">
+        <is>
+          <t>usuario</t>
+        </is>
+      </c>
+    </row>
+    <row r="1316">
+      <c r="A1316" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B1316" t="inlineStr">
+        <is>
+          <t>medianoche</t>
+        </is>
+      </c>
+      <c r="C1316" t="inlineStr">
+        <is>
+          <t>ARROZ</t>
+        </is>
+      </c>
+      <c r="D1316" t="n">
+        <v>25</v>
+      </c>
+      <c r="E1316" t="inlineStr">
+        <is>
+          <t>no_dado</t>
+        </is>
+      </c>
+      <c r="F1316" t="inlineStr">
+        <is>
+          <t>usuario</t>
+        </is>
+      </c>
+    </row>
+    <row r="1317">
+      <c r="A1317" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B1317" t="inlineStr">
+        <is>
+          <t>medianoche</t>
+        </is>
+      </c>
+      <c r="C1317" t="inlineStr">
+        <is>
+          <t>CALCIVET</t>
+        </is>
+      </c>
+      <c r="D1317" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E1317" t="inlineStr">
+        <is>
+          <t>dado</t>
+        </is>
+      </c>
+      <c r="F1317" t="inlineStr">
+        <is>
+          <t>usuario</t>
+        </is>
+      </c>
+    </row>
+    <row r="1318">
+      <c r="A1318" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B1318" t="inlineStr">
+        <is>
+          <t>medianoche</t>
+        </is>
+      </c>
+      <c r="C1318" t="inlineStr">
+        <is>
+          <t>SOPA_MORO</t>
+        </is>
+      </c>
+      <c r="D1318" t="inlineStr"/>
+      <c r="E1318" t="inlineStr">
+        <is>
+          <t>no_dado</t>
+        </is>
+      </c>
+      <c r="F1318" t="inlineStr">
+        <is>
+          <t>usuario</t>
+        </is>
+      </c>
+    </row>
+    <row r="1319">
+      <c r="A1319" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B1319" t="inlineStr">
+        <is>
+          <t>medianoche</t>
+        </is>
+      </c>
+      <c r="C1319" t="inlineStr">
+        <is>
+          <t>MANZANA</t>
+        </is>
+      </c>
+      <c r="D1319" t="n">
+        <v>20</v>
+      </c>
+      <c r="E1319" t="inlineStr">
+        <is>
+          <t>dado</t>
+        </is>
+      </c>
+      <c r="F1319" t="inlineStr">
+        <is>
+          <t>usuario</t>
+        </is>
+      </c>
+    </row>
+    <row r="1320">
+      <c r="A1320" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B1320" t="inlineStr">
+        <is>
+          <t>medianoche</t>
+        </is>
+      </c>
+      <c r="C1320" t="inlineStr">
+        <is>
+          <t>BONIATO</t>
+        </is>
+      </c>
+      <c r="D1320" t="n">
+        <v>25</v>
+      </c>
+      <c r="E1320" t="inlineStr">
+        <is>
+          <t>dado</t>
+        </is>
+      </c>
+      <c r="F1320" t="inlineStr">
+        <is>
+          <t>usuario</t>
+        </is>
+      </c>
+    </row>
+    <row r="1321">
+      <c r="A1321" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B1321" t="inlineStr">
+        <is>
+          <t>medianoche</t>
+        </is>
+      </c>
+      <c r="C1321" t="inlineStr">
+        <is>
+          <t>CERDO</t>
+        </is>
+      </c>
+      <c r="D1321" t="n">
+        <v>125</v>
+      </c>
+      <c r="E1321" t="inlineStr">
+        <is>
+          <t>dado</t>
+        </is>
+      </c>
+      <c r="F1321" t="inlineStr">
+        <is>
+          <t>usuario</t>
+        </is>
+      </c>
+    </row>
+    <row r="1322">
+      <c r="A1322" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B1322" t="inlineStr">
+        <is>
+          <t>mediodia</t>
+        </is>
+      </c>
+      <c r="C1322" t="inlineStr">
+        <is>
+          <t>PECHUGA</t>
+        </is>
+      </c>
+      <c r="D1322" t="n">
+        <v>100</v>
+      </c>
+      <c r="E1322" t="inlineStr">
+        <is>
+          <t>no_dado</t>
+        </is>
+      </c>
+      <c r="F1322" t="inlineStr">
+        <is>
+          <t>usuario</t>
+        </is>
+      </c>
+    </row>
+    <row r="1323">
+      <c r="A1323" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B1323" t="inlineStr">
+        <is>
+          <t>mediodia</t>
+        </is>
+      </c>
+      <c r="C1323" t="inlineStr">
+        <is>
+          <t>MUSLO</t>
+        </is>
+      </c>
+      <c r="D1323" t="n">
+        <v>25</v>
+      </c>
+      <c r="E1323" t="inlineStr">
+        <is>
+          <t>no_dado</t>
+        </is>
+      </c>
+      <c r="F1323" t="inlineStr">
+        <is>
+          <t>usuario</t>
+        </is>
+      </c>
+    </row>
+    <row r="1324">
+      <c r="A1324" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B1324" t="inlineStr">
+        <is>
+          <t>mediodia</t>
+        </is>
+      </c>
+      <c r="C1324" t="inlineStr">
+        <is>
+          <t>ZAPALLITO</t>
+        </is>
+      </c>
+      <c r="D1324" t="n">
+        <v>25</v>
+      </c>
+      <c r="E1324" t="inlineStr">
+        <is>
+          <t>no_dado</t>
+        </is>
+      </c>
+      <c r="F1324" t="inlineStr">
+        <is>
+          <t>usuario</t>
+        </is>
+      </c>
+    </row>
+    <row r="1325">
+      <c r="A1325" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B1325" t="inlineStr">
+        <is>
+          <t>mediodia</t>
+        </is>
+      </c>
+      <c r="C1325" t="inlineStr">
+        <is>
+          <t>ARROZ</t>
+        </is>
+      </c>
+      <c r="D1325" t="n">
+        <v>25</v>
+      </c>
+      <c r="E1325" t="inlineStr">
+        <is>
+          <t>no_dado</t>
+        </is>
+      </c>
+      <c r="F1325" t="inlineStr">
+        <is>
+          <t>usuario</t>
+        </is>
+      </c>
+    </row>
+    <row r="1326">
+      <c r="A1326" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B1326" t="inlineStr">
+        <is>
+          <t>mediodia</t>
+        </is>
+      </c>
+      <c r="C1326" t="inlineStr">
+        <is>
+          <t>JUREL</t>
+        </is>
+      </c>
+      <c r="D1326" t="n">
+        <v>25</v>
+      </c>
+      <c r="E1326" t="inlineStr">
+        <is>
+          <t>no_dado</t>
+        </is>
+      </c>
+      <c r="F1326" t="inlineStr">
+        <is>
+          <t>usuario</t>
+        </is>
+      </c>
+    </row>
+    <row r="1327">
+      <c r="A1327" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B1327" t="inlineStr">
+        <is>
+          <t>mediodia</t>
+        </is>
+      </c>
+      <c r="C1327" t="inlineStr">
+        <is>
+          <t>CALCIVET</t>
+        </is>
+      </c>
+      <c r="D1327" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E1327" t="inlineStr">
+        <is>
+          <t>dado</t>
+        </is>
+      </c>
+      <c r="F1327" t="inlineStr">
+        <is>
+          <t>usuario</t>
+        </is>
+      </c>
+    </row>
+    <row r="1328">
+      <c r="A1328" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B1328" t="inlineStr">
+        <is>
+          <t>mediodia</t>
+        </is>
+      </c>
+      <c r="C1328" t="inlineStr">
+        <is>
+          <t>TAURINA</t>
+        </is>
+      </c>
+      <c r="D1328" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="E1328" t="inlineStr">
+        <is>
+          <t>dado</t>
+        </is>
+      </c>
+      <c r="F1328" t="inlineStr">
+        <is>
+          <t>usuario</t>
+        </is>
+      </c>
+    </row>
+    <row r="1329">
+      <c r="A1329" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B1329" t="inlineStr">
+        <is>
+          <t>mediodia</t>
+        </is>
+      </c>
+      <c r="C1329" t="inlineStr">
+        <is>
+          <t>SOPA_MORO</t>
+        </is>
+      </c>
+      <c r="D1329" t="inlineStr"/>
+      <c r="E1329" t="inlineStr">
+        <is>
+          <t>no_dado</t>
+        </is>
+      </c>
+      <c r="F1329" t="inlineStr">
+        <is>
+          <t>usuario</t>
+        </is>
+      </c>
+    </row>
+    <row r="1330">
+      <c r="A1330" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B1330" t="inlineStr">
+        <is>
+          <t>mediodia</t>
+        </is>
+      </c>
+      <c r="C1330" t="inlineStr">
+        <is>
+          <t>MANZANA</t>
+        </is>
+      </c>
+      <c r="D1330" t="n">
+        <v>20</v>
+      </c>
+      <c r="E1330" t="inlineStr">
+        <is>
+          <t>dado</t>
+        </is>
+      </c>
+      <c r="F1330" t="inlineStr">
+        <is>
+          <t>usuario</t>
+        </is>
+      </c>
+    </row>
+    <row r="1331">
+      <c r="A1331" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B1331" t="inlineStr">
+        <is>
+          <t>mediodia</t>
+        </is>
+      </c>
+      <c r="C1331" t="inlineStr">
+        <is>
+          <t>BONIATO</t>
+        </is>
+      </c>
+      <c r="D1331" t="n">
+        <v>25</v>
+      </c>
+      <c r="E1331" t="inlineStr">
+        <is>
+          <t>dado</t>
+        </is>
+      </c>
+      <c r="F1331" t="inlineStr">
+        <is>
+          <t>usuario</t>
+        </is>
+      </c>
+    </row>
+    <row r="1332">
+      <c r="A1332" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B1332" t="inlineStr">
+        <is>
+          <t>mediodia</t>
+        </is>
+      </c>
+      <c r="C1332" t="inlineStr">
+        <is>
+          <t>CERDO</t>
+        </is>
+      </c>
+      <c r="D1332" t="n">
+        <v>125</v>
+      </c>
+      <c r="E1332" t="inlineStr">
+        <is>
+          <t>dado</t>
+        </is>
+      </c>
+      <c r="F1332" t="inlineStr">
+        <is>
+          <t>usuario</t>
+        </is>
+      </c>
+    </row>
+    <row r="1333">
+      <c r="A1333" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B1333" t="inlineStr">
+        <is>
+          <t>medianoche</t>
+        </is>
+      </c>
+      <c r="C1333" t="inlineStr">
+        <is>
+          <t>PECHUGA</t>
+        </is>
+      </c>
+      <c r="D1333" t="n">
+        <v>100</v>
+      </c>
+      <c r="E1333" t="inlineStr">
+        <is>
+          <t>no_dado</t>
+        </is>
+      </c>
+      <c r="F1333" t="inlineStr">
+        <is>
+          <t>usuario</t>
+        </is>
+      </c>
+    </row>
+    <row r="1334">
+      <c r="A1334" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B1334" t="inlineStr">
+        <is>
+          <t>medianoche</t>
+        </is>
+      </c>
+      <c r="C1334" t="inlineStr">
+        <is>
+          <t>MUSLO</t>
+        </is>
+      </c>
+      <c r="D1334" t="n">
+        <v>25</v>
+      </c>
+      <c r="E1334" t="inlineStr">
+        <is>
+          <t>no_dado</t>
+        </is>
+      </c>
+      <c r="F1334" t="inlineStr">
+        <is>
+          <t>usuario</t>
+        </is>
+      </c>
+    </row>
+    <row r="1335">
+      <c r="A1335" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B1335" t="inlineStr">
+        <is>
+          <t>medianoche</t>
+        </is>
+      </c>
+      <c r="C1335" t="inlineStr">
+        <is>
+          <t>ZAPALLITO</t>
+        </is>
+      </c>
+      <c r="D1335" t="n">
+        <v>25</v>
+      </c>
+      <c r="E1335" t="inlineStr">
+        <is>
+          <t>no_dado</t>
+        </is>
+      </c>
+      <c r="F1335" t="inlineStr">
+        <is>
+          <t>usuario</t>
+        </is>
+      </c>
+    </row>
+    <row r="1336">
+      <c r="A1336" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B1336" t="inlineStr">
+        <is>
+          <t>medianoche</t>
+        </is>
+      </c>
+      <c r="C1336" t="inlineStr">
+        <is>
+          <t>ARROZ</t>
+        </is>
+      </c>
+      <c r="D1336" t="n">
+        <v>25</v>
+      </c>
+      <c r="E1336" t="inlineStr">
+        <is>
+          <t>no_dado</t>
+        </is>
+      </c>
+      <c r="F1336" t="inlineStr">
+        <is>
+          <t>usuario</t>
+        </is>
+      </c>
+    </row>
+    <row r="1337">
+      <c r="A1337" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B1337" t="inlineStr">
+        <is>
+          <t>medianoche</t>
+        </is>
+      </c>
+      <c r="C1337" t="inlineStr">
+        <is>
+          <t>CALCIVET</t>
+        </is>
+      </c>
+      <c r="D1337" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E1337" t="inlineStr">
+        <is>
+          <t>dado</t>
+        </is>
+      </c>
+      <c r="F1337" t="inlineStr">
+        <is>
+          <t>usuario</t>
+        </is>
+      </c>
+    </row>
+    <row r="1338">
+      <c r="A1338" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B1338" t="inlineStr">
+        <is>
+          <t>medianoche</t>
+        </is>
+      </c>
+      <c r="C1338" t="inlineStr">
+        <is>
+          <t>SOPA_MORO</t>
+        </is>
+      </c>
+      <c r="D1338" t="inlineStr"/>
+      <c r="E1338" t="inlineStr">
+        <is>
+          <t>no_dado</t>
+        </is>
+      </c>
+      <c r="F1338" t="inlineStr">
+        <is>
+          <t>usuario</t>
+        </is>
+      </c>
+    </row>
+    <row r="1339">
+      <c r="A1339" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B1339" t="inlineStr">
+        <is>
+          <t>medianoche</t>
+        </is>
+      </c>
+      <c r="C1339" t="inlineStr">
+        <is>
+          <t>MANZANA</t>
+        </is>
+      </c>
+      <c r="D1339" t="n">
+        <v>20</v>
+      </c>
+      <c r="E1339" t="inlineStr">
+        <is>
+          <t>dado</t>
+        </is>
+      </c>
+      <c r="F1339" t="inlineStr">
+        <is>
+          <t>usuario</t>
+        </is>
+      </c>
+    </row>
+    <row r="1340">
+      <c r="A1340" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B1340" t="inlineStr">
+        <is>
+          <t>medianoche</t>
+        </is>
+      </c>
+      <c r="C1340" t="inlineStr">
+        <is>
+          <t>BONIATO</t>
+        </is>
+      </c>
+      <c r="D1340" t="n">
+        <v>25</v>
+      </c>
+      <c r="E1340" t="inlineStr">
+        <is>
+          <t>dado</t>
+        </is>
+      </c>
+      <c r="F1340" t="inlineStr">
+        <is>
+          <t>usuario</t>
+        </is>
+      </c>
+    </row>
+    <row r="1341">
+      <c r="A1341" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B1341" t="inlineStr">
+        <is>
+          <t>medianoche</t>
+        </is>
+      </c>
+      <c r="C1341" t="inlineStr">
+        <is>
+          <t>CERDO</t>
+        </is>
+      </c>
+      <c r="D1341" t="n">
+        <v>125</v>
+      </c>
+      <c r="E1341" t="inlineStr">
+        <is>
+          <t>dado</t>
+        </is>
+      </c>
+      <c r="F1341" t="inlineStr">
+        <is>
+          <t>usuario</t>
+        </is>
+      </c>
+    </row>
+    <row r="1342">
+      <c r="A1342" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B1342" t="inlineStr">
+        <is>
+          <t>mediodia</t>
+        </is>
+      </c>
+      <c r="C1342" t="inlineStr">
+        <is>
+          <t>PECHUGA</t>
+        </is>
+      </c>
+      <c r="D1342" t="n">
+        <v>100</v>
+      </c>
+      <c r="E1342" t="inlineStr">
+        <is>
+          <t>no_dado</t>
+        </is>
+      </c>
+      <c r="F1342" t="inlineStr">
+        <is>
+          <t>usuario</t>
+        </is>
+      </c>
+    </row>
+    <row r="1343">
+      <c r="A1343" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B1343" t="inlineStr">
+        <is>
+          <t>mediodia</t>
+        </is>
+      </c>
+      <c r="C1343" t="inlineStr">
+        <is>
+          <t>MUSLO</t>
+        </is>
+      </c>
+      <c r="D1343" t="n">
+        <v>25</v>
+      </c>
+      <c r="E1343" t="inlineStr">
+        <is>
+          <t>no_dado</t>
+        </is>
+      </c>
+      <c r="F1343" t="inlineStr">
+        <is>
+          <t>usuario</t>
+        </is>
+      </c>
+    </row>
+    <row r="1344">
+      <c r="A1344" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B1344" t="inlineStr">
+        <is>
+          <t>mediodia</t>
+        </is>
+      </c>
+      <c r="C1344" t="inlineStr">
+        <is>
+          <t>ZAPALLITO</t>
+        </is>
+      </c>
+      <c r="D1344" t="n">
+        <v>25</v>
+      </c>
+      <c r="E1344" t="inlineStr">
+        <is>
+          <t>no_dado</t>
+        </is>
+      </c>
+      <c r="F1344" t="inlineStr">
+        <is>
+          <t>usuario</t>
+        </is>
+      </c>
+    </row>
+    <row r="1345">
+      <c r="A1345" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B1345" t="inlineStr">
+        <is>
+          <t>mediodia</t>
+        </is>
+      </c>
+      <c r="C1345" t="inlineStr">
+        <is>
+          <t>ARROZ</t>
+        </is>
+      </c>
+      <c r="D1345" t="n">
+        <v>25</v>
+      </c>
+      <c r="E1345" t="inlineStr">
+        <is>
+          <t>no_dado</t>
+        </is>
+      </c>
+      <c r="F1345" t="inlineStr">
+        <is>
+          <t>usuario</t>
+        </is>
+      </c>
+    </row>
+    <row r="1346">
+      <c r="A1346" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B1346" t="inlineStr">
+        <is>
+          <t>mediodia</t>
+        </is>
+      </c>
+      <c r="C1346" t="inlineStr">
+        <is>
+          <t>JUREL</t>
+        </is>
+      </c>
+      <c r="D1346" t="n">
+        <v>25</v>
+      </c>
+      <c r="E1346" t="inlineStr">
+        <is>
+          <t>no_dado</t>
+        </is>
+      </c>
+      <c r="F1346" t="inlineStr">
+        <is>
+          <t>usuario</t>
+        </is>
+      </c>
+    </row>
+    <row r="1347">
+      <c r="A1347" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B1347" t="inlineStr">
+        <is>
+          <t>mediodia</t>
+        </is>
+      </c>
+      <c r="C1347" t="inlineStr">
+        <is>
+          <t>CALCIVET</t>
+        </is>
+      </c>
+      <c r="D1347" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E1347" t="inlineStr">
+        <is>
+          <t>dado</t>
+        </is>
+      </c>
+      <c r="F1347" t="inlineStr">
+        <is>
+          <t>usuario</t>
+        </is>
+      </c>
+    </row>
+    <row r="1348">
+      <c r="A1348" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B1348" t="inlineStr">
+        <is>
+          <t>mediodia</t>
+        </is>
+      </c>
+      <c r="C1348" t="inlineStr">
+        <is>
+          <t>TAURINA</t>
+        </is>
+      </c>
+      <c r="D1348" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="E1348" t="inlineStr">
+        <is>
+          <t>dado</t>
+        </is>
+      </c>
+      <c r="F1348" t="inlineStr">
+        <is>
+          <t>usuario</t>
+        </is>
+      </c>
+    </row>
+    <row r="1349">
+      <c r="A1349" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B1349" t="inlineStr">
+        <is>
+          <t>mediodia</t>
+        </is>
+      </c>
+      <c r="C1349" t="inlineStr">
+        <is>
+          <t>SOPA_MORO</t>
+        </is>
+      </c>
+      <c r="D1349" t="inlineStr"/>
+      <c r="E1349" t="inlineStr">
+        <is>
+          <t>no_dado</t>
+        </is>
+      </c>
+      <c r="F1349" t="inlineStr">
+        <is>
+          <t>usuario</t>
+        </is>
+      </c>
+    </row>
+    <row r="1350">
+      <c r="A1350" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B1350" t="inlineStr">
+        <is>
+          <t>mediodia</t>
+        </is>
+      </c>
+      <c r="C1350" t="inlineStr">
+        <is>
+          <t>MANZANA</t>
+        </is>
+      </c>
+      <c r="D1350" t="n">
+        <v>20</v>
+      </c>
+      <c r="E1350" t="inlineStr">
+        <is>
+          <t>dado</t>
+        </is>
+      </c>
+      <c r="F1350" t="inlineStr">
+        <is>
+          <t>usuario</t>
+        </is>
+      </c>
+    </row>
+    <row r="1351">
+      <c r="A1351" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B1351" t="inlineStr">
+        <is>
+          <t>mediodia</t>
+        </is>
+      </c>
+      <c r="C1351" t="inlineStr">
+        <is>
+          <t>BONIATO</t>
+        </is>
+      </c>
+      <c r="D1351" t="n">
+        <v>25</v>
+      </c>
+      <c r="E1351" t="inlineStr">
+        <is>
+          <t>dado</t>
+        </is>
+      </c>
+      <c r="F1351" t="inlineStr">
+        <is>
+          <t>usuario</t>
+        </is>
+      </c>
+    </row>
+    <row r="1352">
+      <c r="A1352" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B1352" t="inlineStr">
+        <is>
+          <t>mediodia</t>
+        </is>
+      </c>
+      <c r="C1352" t="inlineStr">
+        <is>
+          <t>CERDO</t>
+        </is>
+      </c>
+      <c r="D1352" t="n">
+        <v>125</v>
+      </c>
+      <c r="E1352" t="inlineStr">
+        <is>
+          <t>dado</t>
+        </is>
+      </c>
+      <c r="F1352" t="inlineStr">
+        <is>
+          <t>usuario</t>
+        </is>
+      </c>
+    </row>
+    <row r="1353">
+      <c r="A1353" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B1353" t="inlineStr">
+        <is>
+          <t>medianoche</t>
+        </is>
+      </c>
+      <c r="C1353" t="inlineStr">
+        <is>
+          <t>PECHUGA</t>
+        </is>
+      </c>
+      <c r="D1353" t="n">
+        <v>100</v>
+      </c>
+      <c r="E1353" t="inlineStr">
+        <is>
+          <t>no_dado</t>
+        </is>
+      </c>
+      <c r="F1353" t="inlineStr">
+        <is>
+          <t>usuario</t>
+        </is>
+      </c>
+    </row>
+    <row r="1354">
+      <c r="A1354" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B1354" t="inlineStr">
+        <is>
+          <t>medianoche</t>
+        </is>
+      </c>
+      <c r="C1354" t="inlineStr">
+        <is>
+          <t>MUSLO</t>
+        </is>
+      </c>
+      <c r="D1354" t="n">
+        <v>25</v>
+      </c>
+      <c r="E1354" t="inlineStr">
+        <is>
+          <t>no_dado</t>
+        </is>
+      </c>
+      <c r="F1354" t="inlineStr">
+        <is>
+          <t>usuario</t>
+        </is>
+      </c>
+    </row>
+    <row r="1355">
+      <c r="A1355" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B1355" t="inlineStr">
+        <is>
+          <t>medianoche</t>
+        </is>
+      </c>
+      <c r="C1355" t="inlineStr">
+        <is>
+          <t>ZAPALLITO</t>
+        </is>
+      </c>
+      <c r="D1355" t="n">
+        <v>25</v>
+      </c>
+      <c r="E1355" t="inlineStr">
+        <is>
+          <t>no_dado</t>
+        </is>
+      </c>
+      <c r="F1355" t="inlineStr">
+        <is>
+          <t>usuario</t>
+        </is>
+      </c>
+    </row>
+    <row r="1356">
+      <c r="A1356" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B1356" t="inlineStr">
+        <is>
+          <t>medianoche</t>
+        </is>
+      </c>
+      <c r="C1356" t="inlineStr">
+        <is>
+          <t>ARROZ</t>
+        </is>
+      </c>
+      <c r="D1356" t="n">
+        <v>25</v>
+      </c>
+      <c r="E1356" t="inlineStr">
+        <is>
+          <t>no_dado</t>
+        </is>
+      </c>
+      <c r="F1356" t="inlineStr">
+        <is>
+          <t>usuario</t>
+        </is>
+      </c>
+    </row>
+    <row r="1357">
+      <c r="A1357" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B1357" t="inlineStr">
+        <is>
+          <t>medianoche</t>
+        </is>
+      </c>
+      <c r="C1357" t="inlineStr">
+        <is>
+          <t>CALCIVET</t>
+        </is>
+      </c>
+      <c r="D1357" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E1357" t="inlineStr">
+        <is>
+          <t>dado</t>
+        </is>
+      </c>
+      <c r="F1357" t="inlineStr">
+        <is>
+          <t>usuario</t>
+        </is>
+      </c>
+    </row>
+    <row r="1358">
+      <c r="A1358" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B1358" t="inlineStr">
+        <is>
+          <t>medianoche</t>
+        </is>
+      </c>
+      <c r="C1358" t="inlineStr">
+        <is>
+          <t>SOPA_MORO</t>
+        </is>
+      </c>
+      <c r="D1358" t="inlineStr"/>
+      <c r="E1358" t="inlineStr">
+        <is>
+          <t>no_dado</t>
+        </is>
+      </c>
+      <c r="F1358" t="inlineStr">
+        <is>
+          <t>usuario</t>
+        </is>
+      </c>
+    </row>
+    <row r="1359">
+      <c r="A1359" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B1359" t="inlineStr">
+        <is>
+          <t>medianoche</t>
+        </is>
+      </c>
+      <c r="C1359" t="inlineStr">
+        <is>
+          <t>MANZANA</t>
+        </is>
+      </c>
+      <c r="D1359" t="n">
+        <v>20</v>
+      </c>
+      <c r="E1359" t="inlineStr">
+        <is>
+          <t>dado</t>
+        </is>
+      </c>
+      <c r="F1359" t="inlineStr">
+        <is>
+          <t>usuario</t>
+        </is>
+      </c>
+    </row>
+    <row r="1360">
+      <c r="A1360" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B1360" t="inlineStr">
+        <is>
+          <t>medianoche</t>
+        </is>
+      </c>
+      <c r="C1360" t="inlineStr">
+        <is>
+          <t>BONIATO</t>
+        </is>
+      </c>
+      <c r="D1360" t="n">
+        <v>25</v>
+      </c>
+      <c r="E1360" t="inlineStr">
+        <is>
+          <t>dado</t>
+        </is>
+      </c>
+      <c r="F1360" t="inlineStr">
+        <is>
+          <t>usuario</t>
+        </is>
+      </c>
+    </row>
+    <row r="1361">
+      <c r="A1361" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B1361" t="inlineStr">
+        <is>
+          <t>medianoche</t>
+        </is>
+      </c>
+      <c r="C1361" t="inlineStr">
+        <is>
+          <t>CERDO</t>
+        </is>
+      </c>
+      <c r="D1361" t="n">
+        <v>125</v>
+      </c>
+      <c r="E1361" t="inlineStr">
+        <is>
+          <t>dado</t>
+        </is>
+      </c>
+      <c r="F1361" t="inlineStr">
+        <is>
+          <t>usuario</t>
+        </is>
+      </c>
+    </row>
+    <row r="1362">
+      <c r="A1362" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B1362" t="inlineStr">
+        <is>
+          <t>mediodia</t>
+        </is>
+      </c>
+      <c r="C1362" t="inlineStr">
+        <is>
+          <t>PECHUGA</t>
+        </is>
+      </c>
+      <c r="D1362" t="n">
+        <v>100</v>
+      </c>
+      <c r="E1362" t="inlineStr">
+        <is>
+          <t>no_dado</t>
+        </is>
+      </c>
+      <c r="F1362" t="inlineStr">
+        <is>
+          <t>usuario</t>
+        </is>
+      </c>
+    </row>
+    <row r="1363">
+      <c r="A1363" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B1363" t="inlineStr">
+        <is>
+          <t>mediodia</t>
+        </is>
+      </c>
+      <c r="C1363" t="inlineStr">
+        <is>
+          <t>MUSLO</t>
+        </is>
+      </c>
+      <c r="D1363" t="n">
+        <v>25</v>
+      </c>
+      <c r="E1363" t="inlineStr">
+        <is>
+          <t>no_dado</t>
+        </is>
+      </c>
+      <c r="F1363" t="inlineStr">
+        <is>
+          <t>usuario</t>
+        </is>
+      </c>
+    </row>
+    <row r="1364">
+      <c r="A1364" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B1364" t="inlineStr">
+        <is>
+          <t>mediodia</t>
+        </is>
+      </c>
+      <c r="C1364" t="inlineStr">
+        <is>
+          <t>ZAPALLITO</t>
+        </is>
+      </c>
+      <c r="D1364" t="n">
+        <v>25</v>
+      </c>
+      <c r="E1364" t="inlineStr">
+        <is>
+          <t>no_dado</t>
+        </is>
+      </c>
+      <c r="F1364" t="inlineStr">
+        <is>
+          <t>usuario</t>
+        </is>
+      </c>
+    </row>
+    <row r="1365">
+      <c r="A1365" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B1365" t="inlineStr">
+        <is>
+          <t>mediodia</t>
+        </is>
+      </c>
+      <c r="C1365" t="inlineStr">
+        <is>
+          <t>ARROZ</t>
+        </is>
+      </c>
+      <c r="D1365" t="n">
+        <v>25</v>
+      </c>
+      <c r="E1365" t="inlineStr">
+        <is>
+          <t>no_dado</t>
+        </is>
+      </c>
+      <c r="F1365" t="inlineStr">
+        <is>
+          <t>usuario</t>
+        </is>
+      </c>
+    </row>
+    <row r="1366">
+      <c r="A1366" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B1366" t="inlineStr">
+        <is>
+          <t>mediodia</t>
+        </is>
+      </c>
+      <c r="C1366" t="inlineStr">
+        <is>
+          <t>JUREL</t>
+        </is>
+      </c>
+      <c r="D1366" t="n">
+        <v>25</v>
+      </c>
+      <c r="E1366" t="inlineStr">
+        <is>
+          <t>no_dado</t>
+        </is>
+      </c>
+      <c r="F1366" t="inlineStr">
+        <is>
+          <t>usuario</t>
+        </is>
+      </c>
+    </row>
+    <row r="1367">
+      <c r="A1367" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B1367" t="inlineStr">
+        <is>
+          <t>mediodia</t>
+        </is>
+      </c>
+      <c r="C1367" t="inlineStr">
+        <is>
+          <t>CALCIVET</t>
+        </is>
+      </c>
+      <c r="D1367" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E1367" t="inlineStr">
+        <is>
+          <t>dado</t>
+        </is>
+      </c>
+      <c r="F1367" t="inlineStr">
+        <is>
+          <t>usuario</t>
+        </is>
+      </c>
+    </row>
+    <row r="1368">
+      <c r="A1368" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B1368" t="inlineStr">
+        <is>
+          <t>mediodia</t>
+        </is>
+      </c>
+      <c r="C1368" t="inlineStr">
+        <is>
+          <t>TAURINA</t>
+        </is>
+      </c>
+      <c r="D1368" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="E1368" t="inlineStr">
+        <is>
+          <t>dado</t>
+        </is>
+      </c>
+      <c r="F1368" t="inlineStr">
+        <is>
+          <t>usuario</t>
+        </is>
+      </c>
+    </row>
+    <row r="1369">
+      <c r="A1369" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B1369" t="inlineStr">
+        <is>
+          <t>mediodia</t>
+        </is>
+      </c>
+      <c r="C1369" t="inlineStr">
+        <is>
+          <t>SOPA_MORO</t>
+        </is>
+      </c>
+      <c r="D1369" t="inlineStr"/>
+      <c r="E1369" t="inlineStr">
+        <is>
+          <t>no_dado</t>
+        </is>
+      </c>
+      <c r="F1369" t="inlineStr">
+        <is>
+          <t>usuario</t>
+        </is>
+      </c>
+    </row>
+    <row r="1370">
+      <c r="A1370" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B1370" t="inlineStr">
+        <is>
+          <t>mediodia</t>
+        </is>
+      </c>
+      <c r="C1370" t="inlineStr">
+        <is>
+          <t>MANZANA</t>
+        </is>
+      </c>
+      <c r="D1370" t="n">
+        <v>20</v>
+      </c>
+      <c r="E1370" t="inlineStr">
+        <is>
+          <t>dado</t>
+        </is>
+      </c>
+      <c r="F1370" t="inlineStr">
+        <is>
+          <t>usuario</t>
+        </is>
+      </c>
+    </row>
+    <row r="1371">
+      <c r="A1371" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B1371" t="inlineStr">
+        <is>
+          <t>mediodia</t>
+        </is>
+      </c>
+      <c r="C1371" t="inlineStr">
+        <is>
+          <t>BONIATO</t>
+        </is>
+      </c>
+      <c r="D1371" t="n">
+        <v>25</v>
+      </c>
+      <c r="E1371" t="inlineStr">
+        <is>
+          <t>dado</t>
+        </is>
+      </c>
+      <c r="F1371" t="inlineStr">
+        <is>
+          <t>usuario</t>
+        </is>
+      </c>
+    </row>
+    <row r="1372">
+      <c r="A1372" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B1372" t="inlineStr">
+        <is>
+          <t>mediodia</t>
+        </is>
+      </c>
+      <c r="C1372" t="inlineStr">
+        <is>
+          <t>CERDO</t>
+        </is>
+      </c>
+      <c r="D1372" t="n">
+        <v>125</v>
+      </c>
+      <c r="E1372" t="inlineStr">
+        <is>
+          <t>dado</t>
+        </is>
+      </c>
+      <c r="F1372" t="inlineStr">
+        <is>
+          <t>usuario</t>
+        </is>
+      </c>
+    </row>
+    <row r="1373">
+      <c r="A1373" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B1373" t="inlineStr">
+        <is>
+          <t>medianoche</t>
+        </is>
+      </c>
+      <c r="C1373" t="inlineStr">
+        <is>
+          <t>PECHUGA</t>
+        </is>
+      </c>
+      <c r="D1373" t="n">
+        <v>100</v>
+      </c>
+      <c r="E1373" t="inlineStr">
+        <is>
+          <t>no_dado</t>
+        </is>
+      </c>
+      <c r="F1373" t="inlineStr">
+        <is>
+          <t>usuario</t>
+        </is>
+      </c>
+    </row>
+    <row r="1374">
+      <c r="A1374" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B1374" t="inlineStr">
+        <is>
+          <t>medianoche</t>
+        </is>
+      </c>
+      <c r="C1374" t="inlineStr">
+        <is>
+          <t>MUSLO</t>
+        </is>
+      </c>
+      <c r="D1374" t="n">
+        <v>25</v>
+      </c>
+      <c r="E1374" t="inlineStr">
+        <is>
+          <t>no_dado</t>
+        </is>
+      </c>
+      <c r="F1374" t="inlineStr">
+        <is>
+          <t>usuario</t>
+        </is>
+      </c>
+    </row>
+    <row r="1375">
+      <c r="A1375" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B1375" t="inlineStr">
+        <is>
+          <t>medianoche</t>
+        </is>
+      </c>
+      <c r="C1375" t="inlineStr">
+        <is>
+          <t>ZAPALLITO</t>
+        </is>
+      </c>
+      <c r="D1375" t="n">
+        <v>25</v>
+      </c>
+      <c r="E1375" t="inlineStr">
+        <is>
+          <t>no_dado</t>
+        </is>
+      </c>
+      <c r="F1375" t="inlineStr">
+        <is>
+          <t>usuario</t>
+        </is>
+      </c>
+    </row>
+    <row r="1376">
+      <c r="A1376" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B1376" t="inlineStr">
+        <is>
+          <t>medianoche</t>
+        </is>
+      </c>
+      <c r="C1376" t="inlineStr">
+        <is>
+          <t>ARROZ</t>
+        </is>
+      </c>
+      <c r="D1376" t="n">
+        <v>25</v>
+      </c>
+      <c r="E1376" t="inlineStr">
+        <is>
+          <t>no_dado</t>
+        </is>
+      </c>
+      <c r="F1376" t="inlineStr">
+        <is>
+          <t>usuario</t>
+        </is>
+      </c>
+    </row>
+    <row r="1377">
+      <c r="A1377" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B1377" t="inlineStr">
+        <is>
+          <t>medianoche</t>
+        </is>
+      </c>
+      <c r="C1377" t="inlineStr">
+        <is>
+          <t>CALCIVET</t>
+        </is>
+      </c>
+      <c r="D1377" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E1377" t="inlineStr">
+        <is>
+          <t>dado</t>
+        </is>
+      </c>
+      <c r="F1377" t="inlineStr">
+        <is>
+          <t>usuario</t>
+        </is>
+      </c>
+    </row>
+    <row r="1378">
+      <c r="A1378" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B1378" t="inlineStr">
+        <is>
+          <t>medianoche</t>
+        </is>
+      </c>
+      <c r="C1378" t="inlineStr">
+        <is>
+          <t>SOPA_MORO</t>
+        </is>
+      </c>
+      <c r="D1378" t="inlineStr"/>
+      <c r="E1378" t="inlineStr">
+        <is>
+          <t>no_dado</t>
+        </is>
+      </c>
+      <c r="F1378" t="inlineStr">
+        <is>
+          <t>usuario</t>
+        </is>
+      </c>
+    </row>
+    <row r="1379">
+      <c r="A1379" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B1379" t="inlineStr">
+        <is>
+          <t>medianoche</t>
+        </is>
+      </c>
+      <c r="C1379" t="inlineStr">
+        <is>
+          <t>MANZANA</t>
+        </is>
+      </c>
+      <c r="D1379" t="n">
+        <v>20</v>
+      </c>
+      <c r="E1379" t="inlineStr">
+        <is>
+          <t>dado</t>
+        </is>
+      </c>
+      <c r="F1379" t="inlineStr">
+        <is>
+          <t>usuario</t>
+        </is>
+      </c>
+    </row>
+    <row r="1380">
+      <c r="A1380" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B1380" t="inlineStr">
+        <is>
+          <t>medianoche</t>
+        </is>
+      </c>
+      <c r="C1380" t="inlineStr">
+        <is>
+          <t>BONIATO</t>
+        </is>
+      </c>
+      <c r="D1380" t="n">
+        <v>25</v>
+      </c>
+      <c r="E1380" t="inlineStr">
+        <is>
+          <t>dado</t>
+        </is>
+      </c>
+      <c r="F1380" t="inlineStr">
+        <is>
+          <t>usuario</t>
+        </is>
+      </c>
+    </row>
+    <row r="1381">
+      <c r="A1381" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B1381" t="inlineStr">
+        <is>
+          <t>medianoche</t>
+        </is>
+      </c>
+      <c r="C1381" t="inlineStr">
+        <is>
+          <t>CERDO</t>
+        </is>
+      </c>
+      <c r="D1381" t="n">
+        <v>125</v>
+      </c>
+      <c r="E1381" t="inlineStr">
+        <is>
+          <t>dado</t>
+        </is>
+      </c>
+      <c r="F1381" t="inlineStr">
+        <is>
+          <t>usuario</t>
         </is>
       </c>
     </row>
